--- a/vastaanottajat-pohja.xlsx
+++ b/vastaanottajat-pohja.xlsx
@@ -55,7 +55,6 @@
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -67,11 +66,6 @@
       <c r="B1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Sähköposti</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Summa</t>
         </is>
       </c>
     </row>
@@ -86,9 +80,6 @@
           <t xml:space="preserve">matti.meikalainen@example.com</t>
         </is>
       </c>
-      <c r="C2">
-        <v>40</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -100,9 +91,6 @@
         <is>
           <t xml:space="preserve">maija.virtanen@example.com</t>
         </is>
-      </c>
-      <c r="C3">
-        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -116,9 +104,6 @@
           <t xml:space="preserve">omer.akkinen@example.com</t>
         </is>
       </c>
-      <c r="C4">
-        <v>20</v>
-      </c>
     </row>
   </sheetData>
 </worksheet>
